--- a/H2/Governanca/2026-07-21-MINUTA-livro-acionistas-reconstruido.xlsx
+++ b/H2/Governanca/2026-07-21-MINUTA-livro-acionistas-reconstruido.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10458" uniqueCount="4742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10463" uniqueCount="4747">
   <si>
     <t>num</t>
   </si>
@@ -14240,6 +14240,21 @@
   </si>
   <si>
     <t>termo de adesao 2026-12-01 (ASSINADO)</t>
+  </si>
+  <si>
+    <t>JAIR RODRIGUES DE OLIVEIRA JUNIOR</t>
+  </si>
+  <si>
+    <t>055.640.941-82</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Diretor Presidente/fundador - AUSENTE da reconstrucao original (2026-07-21), incluido em 2026-07-23 apos alerta do Gustavo. CPF confirmado em multiplas Atas de AGE e Termos de Transferencia (cedente original de diversas acoes distribuidas a medicos). Quantidade de acoes (2.060) e status (REGISTRADO) informados pelo Gustavo - fonte primaria nao re-verificada por mim.</t>
+  </si>
+  <si>
+    <t>fundador (adicionado 2026-07-23)</t>
   </si>
 </sst>
 </file>
@@ -14579,7 +14594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2233"/>
+  <dimension ref="A1:H2234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -70510,6 +70525,29 @@
         <v>2589</v>
       </c>
     </row>
+    <row r="2234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2234">
+        <v>2233</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>4742</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>4743</v>
+      </c>
+      <c r="D2234">
+        <v>2060</v>
+      </c>
+      <c r="E2234" t="s">
+        <v>4744</v>
+      </c>
+      <c r="F2234" t="s">
+        <v>4745</v>
+      </c>
+      <c r="G2234" t="s">
+        <v>4746</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
